--- a/data/trans_orig/P25C_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dejó de fumar con o sin ayuda específica en 2023</t>
+          <t>Población según si dejó de fumar con o sin ayuda específica en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>366</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103320</t>
+          <t>103456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112075</t>
+          <t>112214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45125</t>
+          <t>45249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150938</t>
+          <t>150730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159943</t>
+          <t>160094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40724</t>
+          <t>39442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46762</t>
+          <t>47029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358219</t>
+          <t>359501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397066</t>
+          <t>397353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70297</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78749</t>
+          <t>78860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435545</t>
+          <t>435278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477804</t>
+          <t>477379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117494</t>
+          <t>118508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131967</t>
+          <t>132567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62281</t>
+          <t>63094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>71420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>185573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202487</t>
+          <t>201268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177126</t>
+          <t>177427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>188688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110733</t>
+          <t>112004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122055</t>
+          <t>122199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293500</t>
+          <t>294060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308501</t>
+          <t>308962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>68636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37995</t>
+          <t>37539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>37461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97483</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>782085</t>
+          <t>780917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>831587</t>
+          <t>834511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299448</t>
+          <t>299904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316454</t>
+          <t>316421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089513</t>
+          <t>1089264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1150053</t>
+          <t>1149535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25C_R_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>108941</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103456</t>
+          <t>110212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>119863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45249</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>156600</t>
+          <t>167907</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150730</t>
+          <t>162149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>160094</t>
+          <t>172036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47029</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>385843</t>
+          <t>157681</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359501</t>
+          <t>149329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397353</t>
+          <t>163241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75467</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70285</t>
+          <t>76423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78860</t>
+          <t>85691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>461310</t>
+          <t>239404</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435278</t>
+          <t>230755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477379</t>
+          <t>246838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>171000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>171000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>171000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>482307</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>482307</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>482307</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>17543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30670</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>126687</t>
+          <t>146374</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118508</t>
+          <t>137452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132567</t>
+          <t>153550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>76133</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71420</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>194770</t>
+          <t>222507</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185573</t>
+          <t>212043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201268</t>
+          <t>230602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141392</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>216243</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216243</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>216243</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,22 +1789,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>184396</t>
+          <t>190686</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177427</t>
+          <t>183429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188688</t>
+          <t>195724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>117698</t>
+          <t>126093</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112004</t>
+          <t>119620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122199</t>
+          <t>130959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>302094</t>
+          <t>316779</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294060</t>
+          <t>308332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308962</t>
+          <t>324665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130044</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130044</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>130044</t>
+          <t>139363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>324749</t>
+          <t>341220</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>324749</t>
+          <t>341220</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>324749</t>
+          <t>341220</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>37460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68636</t>
+          <t>64357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>39748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72222</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>64444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97732</t>
+          <t>96826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>805868</t>
+          <t>611308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>780917</t>
+          <t>595862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>834511</t>
+          <t>622759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>308907</t>
+          <t>335291</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299904</t>
+          <t>326142</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316421</t>
+          <t>343208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1114774</t>
+          <t>946599</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089264</t>
+          <t>929283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1149535</t>
+          <t>961665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>849553</t>
+          <t>660219</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337443</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1186996</t>
+          <t>1026109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
